--- a/survey_templates/050_student_basic_needs_survey--survey_templates.xlsx
+++ b/survey_templates/050_student_basic_needs_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Survey for School Use</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Survey Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This survey is for school use only.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,15 +547,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>student_survey_page</t>
+          <t>basic_needs_question_page</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Student Survey</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What do you need most when you're feeling stressed or overwhelmed?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select one option.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,20 +569,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>student_survey_page_2</t>
+          <t>access_to_food_page</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Student Basic Needs</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Access to Basic Needs</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select one option.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,22 +596,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>student_survey_page_3</t>
+          <t>rating_access_page</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Basic Needs</t>
+          <t>Rate Your Access to Basic Needs</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>How often do you have access to food?</t>
+          <t>Select all that apply.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -611,22 +623,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>student_survey_page_4</t>
+          <t>lacking_basic_needs_page</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Basic Needs</t>
+          <t>Basic Needs I'm Lacking</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>How often do you have access to basic needs?</t>
+          <t>Please specify a basic need.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -643,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>basic_needs_page</t>
+          <t>access_to_shelter_page</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Basic Needs</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Access to Shelter</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select one option.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -666,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>basic_needs_page_2</t>
+          <t>difficulty_accessing_needs_page</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Basic Needs</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Basic Needs I'm Having Difficulty Accessing</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -684,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>basic_needs_page_3</t>
+          <t>challenging_situation_page</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Basic Needs</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Challenging Situation</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please share a situation where you had to choose between basic needs.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -707,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>basic_needs_page_4</t>
+          <t>access_to_care_page</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Basic Needs</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Access To Care Page</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select one option.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -735,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>survey_questions_page</t>
+          <t>suggestions_page</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Survey Questions</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Suggestion</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please suggest an idea to improve access to basic needs.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -753,67 +785,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>survey_questions_page_2</t>
+          <t>satisfaction_page</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Basic Needs</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Satisfaction with Access to Basic Needs</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>survey_questions_page_3</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Basic Needs</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>survey_questions_page_4</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Basic Needs</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -830,12 +820,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -858,476 +848,459 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>student_survey_page_2_choices</t>
+          <t>access_to_food_page_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>student_survey_page_2_choices</t>
+          <t>access_to_food_page_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>student_survey_page_3_choices</t>
+          <t>access_to_food_page_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>student_survey_page_3_choices</t>
+          <t>rating_access_page_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>food</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Food</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>student_survey_page_3_choices</t>
+          <t>rating_access_page_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>shelter</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Shelter</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>student_survey_page_3_choices</t>
+          <t>rating_access_page_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>clothing_and_personal_care</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Clothing and Personal Care</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>student_survey_page_4_choices</t>
+          <t>rating_access_page_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>education_and_job_training</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Education and Job Training</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>student_survey_page_4_choices</t>
+          <t>rating_access_page_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>health_care</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Health Care</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>basic_needs_page_choices</t>
+          <t>rating_access_page_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>basic_needs_page_choices</t>
+          <t>access_to_shelter_page_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>basic_needs_page_choices</t>
+          <t>access_to_shelter_page_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>basic_needs_page_choices</t>
+          <t>access_to_shelter_page_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>basic_needs_page_2_choices</t>
+          <t>difficulty_accessing_needs_page_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>food</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Food</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>basic_needs_page_2_choices</t>
+          <t>difficulty_accessing_needs_page_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>shelter</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Shelter</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>basic_needs_page_3_choices</t>
+          <t>difficulty_accessing_needs_page_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>clothing_and_personal_care</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Clothing and Personal Care</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>basic_needs_page_3_choices</t>
+          <t>difficulty_accessing_needs_page_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>education_and_job_training</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Education and Job Training</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>basic_needs_page_4_choices</t>
+          <t>difficulty_accessing_needs_page_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>health_care</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Health Care</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>basic_needs_page_4_choices</t>
+          <t>difficulty_accessing_needs_page_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>survey_questions_page_2_choices</t>
+          <t>access_to_care_page_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>survey_questions_page_2_choices</t>
+          <t>access_to_care_page_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>survey_questions_page_2_choices</t>
+          <t>access_to_care_page_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>survey_questions_page_2_choices</t>
+          <t>satisfaction_page_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>survey_questions_page_3_choices</t>
+          <t>satisfaction_page_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>survey_questions_page_3_choices</t>
+          <t>satisfaction_page_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>survey_questions_page_4_choices</t>
+          <t>satisfaction_page_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>survey_questions_page_4_choices</t>
+          <t>satisfaction_page_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>survey_questions_page_4_choices</t>
+          <t>satisfaction_page_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>survey_questions_page_4_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>option4</t>
+          <t>None</t>
         </is>
       </c>
     </row>
